--- a/rcads/data/xls/32_CodebookOptionMap.xlsx
+++ b/rcads/data/xls/32_CodebookOptionMap.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="1" r:id="rId1" name="_32_CodebookOptionMap"/>
   </sheets>
   <definedNames>
-    <definedName name="_32_CodebookOptionMap">'_32_CodebookOptionMap'!$A$1:$E$173</definedName>
+    <definedName name="_32_CodebookOptionMap">'_32_CodebookOptionMap'!$A$1:$E$193</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -343,7 +343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E173"/>
+  <dimension ref="A1:E193"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -3297,6 +3297,346 @@
         <v>3</v>
       </c>
     </row>
+    <row outlineLevel="0" r="174">
+      <c r="A174" s="0">
+        <v>173</v>
+      </c>
+      <c r="B174" s="0">
+        <v>44</v>
+      </c>
+      <c r="C174" s="0">
+        <v>169</v>
+      </c>
+      <c r="D174" s="0">
+        <v>1</v>
+      </c>
+      <c r="E174" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="175">
+      <c r="A175" s="0">
+        <v>174</v>
+      </c>
+      <c r="B175" s="0">
+        <v>44</v>
+      </c>
+      <c r="C175" s="0">
+        <v>170</v>
+      </c>
+      <c r="D175" s="0">
+        <v>2</v>
+      </c>
+      <c r="E175" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="176">
+      <c r="A176" s="0">
+        <v>175</v>
+      </c>
+      <c r="B176" s="0">
+        <v>44</v>
+      </c>
+      <c r="C176" s="0">
+        <v>171</v>
+      </c>
+      <c r="D176" s="0">
+        <v>3</v>
+      </c>
+      <c r="E176" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="177">
+      <c r="A177" s="0">
+        <v>176</v>
+      </c>
+      <c r="B177" s="0">
+        <v>44</v>
+      </c>
+      <c r="C177" s="0">
+        <v>172</v>
+      </c>
+      <c r="D177" s="0">
+        <v>4</v>
+      </c>
+      <c r="E177" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="178">
+      <c r="A178" s="0">
+        <v>177</v>
+      </c>
+      <c r="B178" s="0">
+        <v>45</v>
+      </c>
+      <c r="C178" s="0">
+        <v>173</v>
+      </c>
+      <c r="D178" s="0">
+        <v>1</v>
+      </c>
+      <c r="E178" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="179">
+      <c r="A179" s="0">
+        <v>178</v>
+      </c>
+      <c r="B179" s="0">
+        <v>45</v>
+      </c>
+      <c r="C179" s="0">
+        <v>174</v>
+      </c>
+      <c r="D179" s="0">
+        <v>2</v>
+      </c>
+      <c r="E179" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="180">
+      <c r="A180" s="0">
+        <v>179</v>
+      </c>
+      <c r="B180" s="0">
+        <v>45</v>
+      </c>
+      <c r="C180" s="0">
+        <v>175</v>
+      </c>
+      <c r="D180" s="0">
+        <v>3</v>
+      </c>
+      <c r="E180" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="181">
+      <c r="A181" s="0">
+        <v>180</v>
+      </c>
+      <c r="B181" s="0">
+        <v>45</v>
+      </c>
+      <c r="C181" s="0">
+        <v>176</v>
+      </c>
+      <c r="D181" s="0">
+        <v>4</v>
+      </c>
+      <c r="E181" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="182">
+      <c r="A182" s="0">
+        <v>181</v>
+      </c>
+      <c r="B182" s="0">
+        <v>46</v>
+      </c>
+      <c r="C182" s="0">
+        <v>177</v>
+      </c>
+      <c r="D182" s="0">
+        <v>1</v>
+      </c>
+      <c r="E182" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="183">
+      <c r="A183" s="0">
+        <v>182</v>
+      </c>
+      <c r="B183" s="0">
+        <v>46</v>
+      </c>
+      <c r="C183" s="0">
+        <v>178</v>
+      </c>
+      <c r="D183" s="0">
+        <v>2</v>
+      </c>
+      <c r="E183" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="184">
+      <c r="A184" s="0">
+        <v>183</v>
+      </c>
+      <c r="B184" s="0">
+        <v>46</v>
+      </c>
+      <c r="C184" s="0">
+        <v>179</v>
+      </c>
+      <c r="D184" s="0">
+        <v>3</v>
+      </c>
+      <c r="E184" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="185">
+      <c r="A185" s="0">
+        <v>184</v>
+      </c>
+      <c r="B185" s="0">
+        <v>46</v>
+      </c>
+      <c r="C185" s="0">
+        <v>180</v>
+      </c>
+      <c r="D185" s="0">
+        <v>4</v>
+      </c>
+      <c r="E185" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="186">
+      <c r="A186" s="0">
+        <v>185</v>
+      </c>
+      <c r="B186" s="0">
+        <v>47</v>
+      </c>
+      <c r="C186" s="0">
+        <v>106</v>
+      </c>
+      <c r="D186" s="0">
+        <v>1</v>
+      </c>
+      <c r="E186" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="187">
+      <c r="A187" s="0">
+        <v>186</v>
+      </c>
+      <c r="B187" s="0">
+        <v>47</v>
+      </c>
+      <c r="C187" s="0">
+        <v>107</v>
+      </c>
+      <c r="D187" s="0">
+        <v>2</v>
+      </c>
+      <c r="E187" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="188">
+      <c r="A188" s="0">
+        <v>187</v>
+      </c>
+      <c r="B188" s="0">
+        <v>47</v>
+      </c>
+      <c r="C188" s="0">
+        <v>181</v>
+      </c>
+      <c r="D188" s="0">
+        <v>3</v>
+      </c>
+      <c r="E188" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="189">
+      <c r="A189" s="0">
+        <v>188</v>
+      </c>
+      <c r="B189" s="0">
+        <v>47</v>
+      </c>
+      <c r="C189" s="0">
+        <v>109</v>
+      </c>
+      <c r="D189" s="0">
+        <v>4</v>
+      </c>
+      <c r="E189" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="190">
+      <c r="A190" s="0">
+        <v>189</v>
+      </c>
+      <c r="B190" s="0">
+        <v>48</v>
+      </c>
+      <c r="C190" s="0">
+        <v>182</v>
+      </c>
+      <c r="D190" s="0">
+        <v>1</v>
+      </c>
+      <c r="E190" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="191">
+      <c r="A191" s="0">
+        <v>190</v>
+      </c>
+      <c r="B191" s="0">
+        <v>48</v>
+      </c>
+      <c r="C191" s="0">
+        <v>183</v>
+      </c>
+      <c r="D191" s="0">
+        <v>2</v>
+      </c>
+      <c r="E191" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="192">
+      <c r="A192" s="0">
+        <v>191</v>
+      </c>
+      <c r="B192" s="0">
+        <v>48</v>
+      </c>
+      <c r="C192" s="0">
+        <v>184</v>
+      </c>
+      <c r="D192" s="0">
+        <v>3</v>
+      </c>
+      <c r="E192" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="193">
+      <c r="A193" s="0">
+        <v>192</v>
+      </c>
+      <c r="B193" s="0">
+        <v>48</v>
+      </c>
+      <c r="C193" s="0">
+        <v>185</v>
+      </c>
+      <c r="D193" s="0">
+        <v>4</v>
+      </c>
+      <c r="E193" s="0">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
